--- a/data/export/2026-10-26-operations.xlsx
+++ b/data/export/2026-10-26-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:27</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -908,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +963,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +974,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1040,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1079,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1090,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1123,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1184,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1204,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1280,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1330,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1396,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1446,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1512,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1562,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1575,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1623,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1642,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1678,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1739,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1758,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1794,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1855,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1874,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1910,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1971,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1990,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2015,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2091,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2110,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2146,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2207,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2226,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2262,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2323,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2342,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2367,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2378,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2439,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2483,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2494,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2507,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2555,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2574,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2610,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,7 +2638,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2648,7 +2676,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2698,35 +2726,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2792,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2806,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2842,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2908,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2922,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2958,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3019,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3038,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3074,3603 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-operations.xlsx
+++ b/data/export/2026-10-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -891,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -924,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -948,17 +952,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -968,13 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1090,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1133,24 +1141,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1160,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1199,22 +1207,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1247,32 +1255,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1280,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1304,33 +1316,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1379,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1396,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1420,33 +1440,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1479,32 +1503,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1512,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1536,33 +1564,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1678,7 +1710,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1776,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1794,7 +1826,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1910,7 +1942,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2008,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2030,7 +2062,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2128,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2146,7 +2178,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2244,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2262,7 +2294,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2360,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2372,13 +2404,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2427,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2480,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2458,7 +2494,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,41 +2524,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2555,12 +2595,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2574,7 +2614,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2599,7 +2639,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2610,35 +2650,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2671,12 +2711,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2690,7 +2730,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2715,46 +2755,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2787,12 +2831,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2806,7 +2850,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2842,35 +2886,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2903,12 +2947,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2922,7 +2966,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2947,46 +2991,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3019,12 +3067,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3038,7 +3086,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3063,46 +3111,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3135,12 +3187,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3154,7 +3206,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3179,18 +3231,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3203,52 +3259,56 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3256,7 +3316,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3270,7 +3330,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3280,33 +3340,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3383,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3329,7 +3393,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3339,40 +3403,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3386,7 +3454,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3396,33 +3464,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3507,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3445,7 +3517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3483,12 +3555,12 @@
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3502,7 +3574,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3538,7 +3610,7 @@
       <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3551,60 +3623,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3618,7 +3694,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3628,17 +3704,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3648,13 +3724,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3747,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3715,12 +3795,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3734,7 +3814,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3770,7 +3850,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3783,22 +3863,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3831,12 +3911,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3850,7 +3930,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3886,7 +3966,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3979,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3909,7 +3989,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3947,12 +4027,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3966,7 +4046,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4002,7 +4082,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4015,22 +4095,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4063,12 +4143,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4082,7 +4162,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4118,7 +4198,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4131,22 +4211,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4179,12 +4259,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4198,7 +4278,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4234,7 +4314,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4327,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4257,7 +4337,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4295,12 +4375,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4314,7 +4394,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4350,7 +4430,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4443,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4373,7 +4453,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4411,12 +4491,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4430,7 +4510,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4466,7 +4546,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4479,22 +4559,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4527,12 +4607,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4546,7 +4626,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4582,7 +4662,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4675,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4605,7 +4685,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4643,12 +4723,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4662,7 +4742,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4698,7 +4778,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4791,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4721,7 +4801,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4759,12 +4839,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4778,7 +4858,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4814,35 +4894,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4875,12 +4955,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4894,7 +4974,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4919,7 +4999,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4930,35 +5010,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4991,12 +5071,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5010,7 +5090,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5046,35 +5126,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5107,12 +5187,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5126,7 +5206,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5162,35 +5242,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5228,7 +5308,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5242,7 +5322,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5278,35 +5358,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5339,12 +5419,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5358,7 +5438,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5394,35 +5474,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5455,12 +5535,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5474,7 +5554,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5510,35 +5590,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5571,12 +5651,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5590,7 +5670,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5626,35 +5706,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5687,12 +5767,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5706,7 +5786,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5742,35 +5822,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5803,12 +5883,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5822,7 +5902,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5858,35 +5938,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5919,12 +5999,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5938,7 +6018,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5974,35 +6054,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6035,12 +6115,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6054,7 +6134,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6090,35 +6170,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6151,12 +6231,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6170,7 +6250,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6206,35 +6286,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6267,12 +6347,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6286,7 +6366,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6322,35 +6402,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6383,12 +6463,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6402,7 +6482,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6427,46 +6507,50 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6504,7 +6588,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6518,7 +6602,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6543,18 +6627,22 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB52" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -6572,47 +6660,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6620,7 +6712,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6634,7 +6726,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6644,33 +6736,2721 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
+      <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC53" s="2" t="inlineStr"/>
-      <c r="AD53" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-operations.xlsx
+++ b/data/export/2026-10-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD76"/>
+  <dimension ref="A1:AD78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1389,24 +1389,24 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1743,32 +1743,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1776,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1800,33 +1804,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1900,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2128,7 +2136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2244,7 +2252,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2360,7 +2368,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2480,7 +2488,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2600,7 +2608,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2716,7 +2724,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2836,7 +2844,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2952,7 +2960,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3072,7 +3080,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3121,7 +3129,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3192,7 +3200,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3241,82 +3249,78 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3330,7 +3334,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3340,17 +3344,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3360,87 +3364,79 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3454,7 +3450,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3464,17 +3460,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3489,12 +3485,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3503,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3517,7 +3513,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3527,32 +3523,36 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3584,33 +3584,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3627,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3633,7 +3637,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3653,12 +3657,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -3680,7 +3684,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3694,7 +3698,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3719,17 +3723,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3747,7 +3751,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3757,7 +3761,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3767,32 +3771,36 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3800,7 +3808,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3814,7 +3822,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3824,17 +3832,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3844,13 +3852,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3863,60 +3875,64 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3930,7 +3946,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3940,17 +3956,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3960,13 +3976,17 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3979,22 +3999,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4046,7 +4066,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4095,22 +4115,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4148,7 +4168,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4162,7 +4182,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4211,22 +4231,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4259,12 +4279,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4278,7 +4298,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4327,22 +4347,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4375,12 +4395,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4394,7 +4414,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4443,22 +4463,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4491,12 +4511,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4510,7 +4530,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4559,22 +4579,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4607,12 +4627,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4626,7 +4646,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4675,7 +4695,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4685,7 +4705,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4723,12 +4743,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4742,7 +4762,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4791,22 +4811,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4844,7 +4864,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4858,7 +4878,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4907,7 +4927,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4917,7 +4937,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4955,12 +4975,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4974,7 +4994,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5023,7 +5043,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5033,7 +5053,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5071,12 +5091,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5090,7 +5110,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5139,7 +5159,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5149,7 +5169,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5187,12 +5207,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5206,7 +5226,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5255,7 +5275,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5265,7 +5285,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5303,12 +5323,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5322,7 +5342,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5371,7 +5391,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5381,7 +5401,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5424,7 +5444,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5438,7 +5458,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5487,7 +5507,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5497,7 +5517,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5535,12 +5555,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5554,7 +5574,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5603,7 +5623,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5613,7 +5633,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5651,12 +5671,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5670,7 +5690,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5719,7 +5739,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5729,7 +5749,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5767,12 +5787,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5786,7 +5806,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5835,7 +5855,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5845,7 +5865,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5883,12 +5903,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5902,7 +5922,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5951,7 +5971,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5961,7 +5981,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5999,12 +6019,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6018,7 +6038,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6067,7 +6087,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6077,7 +6097,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6115,12 +6135,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6134,7 +6154,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6183,7 +6203,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6193,7 +6213,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6236,7 +6256,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6250,7 +6270,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6299,7 +6319,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6309,7 +6329,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6347,12 +6367,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6366,7 +6386,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6415,7 +6435,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6425,7 +6445,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6468,7 +6488,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6482,7 +6502,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6507,22 +6527,18 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6551,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6545,7 +6561,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6588,7 +6604,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6602,7 +6618,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6627,84 +6643,76 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6712,7 +6720,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6726,7 +6734,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6736,17 +6744,17 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6761,40 +6769,40 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6832,7 +6840,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6846,7 +6854,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6876,13 +6884,17 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6907,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6905,7 +6917,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6915,32 +6927,36 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6948,7 +6964,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6962,7 +6978,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6972,17 +6988,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6992,13 +7008,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7011,64 +7031,60 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7082,7 +7098,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7092,17 +7108,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7112,17 +7128,13 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7147,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7145,7 +7157,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7183,12 +7195,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7202,7 +7214,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7227,7 +7239,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7251,7 +7263,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7261,7 +7273,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7271,32 +7283,36 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7304,7 +7320,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7318,7 +7334,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7328,17 +7344,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7348,13 +7364,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7367,22 +7387,22 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7415,12 +7435,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7434,7 +7454,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7483,22 +7503,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:52</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7536,7 +7556,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7550,7 +7570,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7575,7 +7595,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7599,7 +7619,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7609,7 +7629,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7647,12 +7667,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7666,7 +7686,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7691,7 +7711,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7715,7 +7735,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7725,7 +7745,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7763,12 +7783,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7782,7 +7802,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7831,22 +7851,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7879,12 +7899,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7898,7 +7918,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7923,7 +7943,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7947,22 +7967,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:29</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7995,7 +8015,7 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8014,7 +8034,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8063,7 +8083,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8073,7 +8093,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8111,12 +8131,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8130,7 +8150,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8179,22 +8199,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8227,12 +8247,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8246,7 +8266,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8295,22 +8315,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8343,12 +8363,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8362,7 +8382,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8411,7 +8431,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A53062D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8421,7 +8441,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8459,12 +8479,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8478,7 +8498,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8527,7 +8547,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8537,7 +8557,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8580,7 +8600,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8594,7 +8614,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8619,22 +8639,18 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8663,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8657,7 +8673,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8695,12 +8711,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8714,7 +8730,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8763,7 +8779,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8773,7 +8789,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8816,7 +8832,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8830,7 +8846,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8860,13 +8876,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8879,7 +8899,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8889,7 +8909,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8927,12 +8947,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8946,7 +8966,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8971,22 +8991,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8999,7 +9015,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9009,7 +9025,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9047,12 +9063,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9066,7 +9082,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9091,7 +9107,7 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9115,22 +9131,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9163,12 +9179,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9182,7 +9198,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9212,13 +9228,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9231,22 +9251,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9279,7 +9299,7 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9298,7 +9318,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9323,7 +9343,7 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9347,22 +9367,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9395,12 +9415,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9414,7 +9434,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9449,6 +9469,238 @@
       </c>
       <c r="AC76" s="2" t="inlineStr"/>
       <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-26-operations.xlsx
+++ b/data/export/2026-10-26-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD78"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1627,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1660,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1684,17 +1688,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1704,13 +1708,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1761,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1780,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1829,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1875,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1900,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1924,33 +1936,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1983,32 +1999,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2016,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2040,37 +2060,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2103,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2136,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2160,33 +2184,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2219,32 +2247,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2252,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2276,33 +2308,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2335,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2368,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2392,37 +2432,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2528,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2542,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2648,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2647,7 +2687,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2724,7 +2764,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2778,7 +2818,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2884,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2960,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3014,7 +3054,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3200,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3320,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3364,13 +3404,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3485,82 +3529,78 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3574,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3584,17 +3624,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3609,82 +3649,78 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3698,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3708,107 +3744,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A32899D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3822,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3832,107 +3864,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3946,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3956,65 +3984,65 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4047,12 +4075,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4066,7 +4094,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4091,46 +4119,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4163,12 +4195,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4182,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4207,7 +4239,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4218,7 +4250,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -4231,52 +4263,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4284,7 +4320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4298,7 +4334,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4308,33 +4344,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4387,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4357,7 +4397,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4367,40 +4407,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4414,7 +4458,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4424,33 +4468,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4511,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4473,7 +4521,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4483,40 +4531,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4530,7 +4582,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4540,33 +4592,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4579,60 +4635,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4646,7 +4706,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4656,33 +4716,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4695,22 +4759,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4743,12 +4807,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4762,7 +4826,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4787,7 +4851,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4811,60 +4875,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4878,7 +4946,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4888,33 +4956,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4999,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4937,7 +5009,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4947,40 +5019,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4994,7 +5070,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5004,33 +5080,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5043,60 +5123,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5110,7 +5194,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5120,33 +5204,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5159,60 +5247,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5226,7 +5318,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5236,33 +5328,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5371,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5285,7 +5381,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5323,12 +5419,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5342,7 +5438,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5367,7 +5463,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5391,7 +5487,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5401,7 +5497,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5439,12 +5535,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5458,7 +5554,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5483,7 +5579,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5507,32 +5603,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5555,12 +5651,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5568,13 +5664,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq22映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5623,7 +5731,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5633,7 +5741,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5671,12 +5779,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5690,7 +5798,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5739,7 +5847,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5749,7 +5857,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5787,12 +5895,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5806,7 +5914,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5855,7 +5963,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5865,7 +5973,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5875,12 +5983,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq39推进至seq49，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5903,12 +6011,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5916,13 +6024,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq39（站名待映射） ETA 3分钟参与校验</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5971,7 +6095,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5981,7 +6105,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6019,12 +6143,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6038,7 +6162,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6087,7 +6211,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6097,7 +6221,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6135,12 +6259,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6154,7 +6278,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6203,7 +6327,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6213,7 +6337,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6251,12 +6375,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6270,7 +6394,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6319,7 +6443,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6329,7 +6453,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6367,12 +6491,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6386,7 +6510,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6435,7 +6559,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6445,7 +6569,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6483,12 +6607,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6502,7 +6626,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6551,7 +6675,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6561,7 +6685,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6599,12 +6723,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6618,7 +6742,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6667,7 +6791,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6677,7 +6801,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6715,12 +6839,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6734,7 +6858,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6759,22 +6883,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6907,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6797,7 +6917,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6840,7 +6960,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6854,7 +6974,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6879,84 +6999,76 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6964,7 +7076,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6978,7 +7090,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6988,65 +7100,61 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7079,12 +7187,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7098,7 +7206,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7123,7 +7231,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7134,35 +7242,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7200,7 +7308,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7214,7 +7322,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7239,7 +7347,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7250,77 +7358,73 @@
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7334,7 +7438,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7344,65 +7448,61 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7435,12 +7535,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7454,7 +7554,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7479,46 +7579,50 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7551,12 +7655,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7570,7 +7674,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7600,41 +7704,45 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7667,12 +7775,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7686,7 +7794,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7711,46 +7819,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7783,12 +7895,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7802,7 +7914,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7827,46 +7939,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7899,12 +8015,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7918,7 +8034,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7954,35 +8070,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8015,12 +8131,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8034,7 +8150,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8059,46 +8175,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8131,12 +8251,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8150,7 +8270,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8175,46 +8295,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8247,12 +8371,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8266,7 +8390,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8291,46 +8415,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8363,12 +8491,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8382,7 +8510,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8407,46 +8535,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A53062D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8479,12 +8611,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8498,7 +8630,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8523,7 +8655,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8534,35 +8666,35 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8595,12 +8727,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8614,7 +8746,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8639,7 +8771,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8650,7 +8782,7 @@
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8795,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8673,7 +8805,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8683,40 +8815,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8730,7 +8866,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8740,33 +8876,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8779,22 +8919,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8832,7 +8972,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8846,7 +8986,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8871,22 +9011,18 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>106.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8899,7 +9035,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8909,7 +9045,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8947,12 +9083,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:53</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8966,7 +9102,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8991,7 +9127,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9015,7 +9151,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9025,7 +9161,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9035,40 +9171,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9082,7 +9222,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9092,17 +9232,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9112,13 +9252,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9275,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9141,7 +9285,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9151,40 +9295,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9198,7 +9346,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9208,17 +9356,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9233,12 +9381,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9399,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9261,7 +9409,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9299,12 +9447,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9318,7 +9466,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9343,7 +9491,7 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
@@ -9367,7 +9515,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9377,7 +9525,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9415,12 +9563,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>06:53</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9434,7 +9582,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9459,7 +9607,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9483,7 +9631,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9493,7 +9641,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9503,32 +9651,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9536,7 +9688,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9550,7 +9702,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9560,17 +9712,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9580,13 +9732,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9604,17 +9760,17 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9652,7 +9808,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9666,7 +9822,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9701,6 +9857,2958 @@
       </c>
       <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53062D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-26-operations.xlsx
+++ b/data/export/2026-10-26-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7532,12 +7532,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10256,17 +10256,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10380,17 +10380,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11561,12 +11561,12 @@
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11663,32 +11663,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11696,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11720,17 +11724,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11740,17 +11744,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11783,32 +11787,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11816,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11840,17 +11848,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11860,12 +11868,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11903,32 +11911,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11936,7 +11948,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11960,17 +11972,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11980,17 +11992,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12176,7 +12188,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12230,7 +12242,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12308,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12416,7 +12428,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12460,17 +12472,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12978,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13164,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13330,7 +13342,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13536,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13648,7 +13660,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13702,7 +13714,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13784,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -14028,7 +14040,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14202,7 +14214,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14280,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14338,7 +14350,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14416,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14528,7 +14540,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14572,17 +14584,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -14772,7 +14784,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14896,7 +14908,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14950,7 +14962,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -15016,7 +15028,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15194,7 +15206,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15276,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15313,12 +15325,12 @@
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15520,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15686,7 +15698,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15800,17 +15812,17 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -16306,7 +16318,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -16492,7 +16504,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16670,7 +16682,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16876,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16988,7 +17000,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17042,7 +17054,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17124,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17286,7 +17298,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -17356,7 +17368,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17480,7 +17492,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17604,7 +17616,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17648,17 +17660,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17864,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17906,7 +17918,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17976,7 +17988,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18154,7 +18166,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -18224,7 +18236,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18402,7 +18414,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18484,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18650,7 +18662,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19088,7 +19100,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19402,7 +19414,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19484,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19526,7 +19538,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19732,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19764,17 +19776,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -19898,7 +19910,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -19968,7 +19980,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20146,7 +20158,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -20394,7 +20406,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20518,7 +20530,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20724,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -21088,7 +21100,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21208,7 +21220,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21328,7 +21340,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21377,12 +21389,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21464,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21576,7 +21588,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21620,17 +21632,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -21700,7 +21712,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21754,7 +21766,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21836,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21948,7 +21960,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22196,7 +22208,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22320,7 +22332,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22374,7 +22386,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -22564,7 +22576,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22742,7 +22754,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -23114,7 +23126,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -23238,7 +23250,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23436,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23478,7 +23490,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -23521,24 +23533,24 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O187" s="2" t="inlineStr">
@@ -23548,7 +23560,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23597,12 +23609,12 @@
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -23635,32 +23647,36 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23668,7 +23684,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23692,17 +23708,17 @@
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA188" s="2" t="inlineStr">
@@ -23712,17 +23728,17 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -23755,32 +23771,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23788,7 +23808,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23812,17 +23832,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23832,17 +23852,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -23908,7 +23928,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23995,12 +24015,12 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -24028,7 +24048,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24036,10 +24056,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R191" s="2" t="inlineStr"/>
-      <c r="S191" s="2" t="inlineStr"/>
-      <c r="T191" s="2" t="inlineStr"/>
-      <c r="U191" s="2" t="inlineStr"/>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V191" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24148,7 +24184,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24268,7 +24304,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24388,7 +24424,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24442,7 +24478,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -24508,7 +24544,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24628,7 +24664,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24748,7 +24784,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24868,7 +24904,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24922,7 +24958,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -24988,7 +25024,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25108,7 +25144,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25162,7 +25198,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -25232,7 +25268,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25286,7 +25322,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -25720,7 +25756,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25840,7 +25876,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25894,7 +25930,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26204,7 +26240,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26248,17 +26284,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26324,7 +26360,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26368,17 +26404,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -26502,7 +26538,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26622,7 +26658,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -27056,7 +27092,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27110,7 +27146,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27180,7 +27216,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27234,7 +27270,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27900,7 +27936,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27954,7 +27990,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28020,7 +28056,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28264,7 +28300,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28308,17 +28344,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28384,7 +28420,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28428,17 +28464,17 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -28562,7 +28598,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -28806,7 +28842,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29124,7 +29160,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29178,7 +29214,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29244,7 +29280,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q234" s="2" t="inlineStr">
@@ -29310,7 +29346,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -29620,7 +29656,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29676,17 +29712,17 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29934,7 +29970,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -30058,7 +30094,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30500,7 +30536,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30554,7 +30590,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30996,7 +31032,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31040,17 +31076,17 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31170,7 +31206,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31294,7 +31330,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31732,7 +31768,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31786,7 +31822,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32352,7 +32388,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32396,17 +32432,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32530,7 +32566,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32848,7 +32884,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33220,7 +33256,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33274,7 +33310,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33344,7 +33380,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33398,7 +33434,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33584,7 +33620,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33628,17 +33664,17 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34494,7 +34530,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34564,7 +34600,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34936,7 +34972,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -34990,7 +35026,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35060,7 +35096,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35114,7 +35150,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35424,7 +35460,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35468,17 +35504,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35792,7 +35828,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35846,7 +35882,7 @@
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36094,7 +36130,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36288,7 +36324,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36397,12 +36433,12 @@
       <c r="L292" s="2" t="inlineStr"/>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N292" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O292" s="2" t="inlineStr">
@@ -36412,7 +36448,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36466,7 +36502,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36499,32 +36535,36 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr"/>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N293" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O293" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -36532,7 +36572,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36556,17 +36596,17 @@
       </c>
       <c r="X293" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y293" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z293" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA293" s="2" t="inlineStr">
@@ -36576,17 +36616,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36619,32 +36659,36 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr"/>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N294" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -36652,7 +36696,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36676,17 +36720,17 @@
       </c>
       <c r="X294" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y294" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z294" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA294" s="2" t="inlineStr">
@@ -36696,17 +36740,17 @@
       </c>
       <c r="AB294" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36772,7 +36816,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36826,7 +36870,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36892,7 +36936,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36946,7 +36990,7 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37012,7 +37056,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37132,7 +37176,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37176,17 +37220,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -37252,7 +37296,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37306,7 +37350,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-26-operations.xlsx
+++ b/data/export/2026-10-26-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4184,17 +4184,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,17 +5548,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,17 +7904,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10708,7 +10708,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11000,17 +11000,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11372,12 +11372,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11921,24 +11921,24 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12035,32 +12035,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12068,7 +12072,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12092,17 +12096,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12112,17 +12116,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -12155,32 +12159,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12188,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12212,17 +12220,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12232,12 +12240,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12308,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12428,7 +12436,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12477,7 +12485,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12730,7 +12738,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12986,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13172,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13218,7 +13226,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13350,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13544,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13580,17 +13588,17 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13668,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13784,7 +13792,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13828,17 +13836,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14048,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14084,17 +14092,17 @@
       </c>
       <c r="AB110" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14424,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14470,7 +14478,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14792,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14908,7 +14916,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15028,7 +15036,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15330,7 +15338,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15520,7 +15528,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15574,7 +15582,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15954,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16318,7 +16326,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16512,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16558,7 +16566,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16682,7 +16690,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -16876,7 +16884,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16920,17 +16928,17 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17008,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17124,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17168,17 +17176,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17368,7 +17376,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17412,17 +17420,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -17492,7 +17500,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17546,7 +17554,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17872,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17988,7 +17996,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18236,7 +18244,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18484,7 +18492,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18538,7 +18546,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -18662,7 +18670,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19988,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20282,7 +20290,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20414,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -20530,7 +20538,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20732,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20768,17 +20776,17 @@
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC164" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21108,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21144,17 +21152,17 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -21220,7 +21228,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21394,7 +21402,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21464,7 +21472,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21836,7 +21844,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21890,7 +21898,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21960,7 +21968,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22004,17 +22012,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -22208,7 +22216,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22262,7 +22270,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22340,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22576,7 +22584,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22630,7 +22638,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -23002,7 +23010,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -23250,7 +23258,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -23436,7 +23444,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23614,7 +23622,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -23895,32 +23903,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23928,7 +23940,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23952,17 +23964,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23972,17 +23984,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.2</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24032,7 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -24048,7 +24060,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24118,7 +24130,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -24151,32 +24163,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -24184,7 +24200,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24208,17 +24224,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24228,17 +24244,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24271,32 +24287,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -24304,7 +24324,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24328,17 +24348,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24348,17 +24368,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -24544,7 +24564,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24664,7 +24684,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24718,7 +24738,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -24784,7 +24804,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24904,7 +24924,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -25024,7 +25044,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25078,7 +25098,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25144,7 +25164,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25268,7 +25288,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25312,17 +25332,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -25686,7 +25706,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -25756,7 +25776,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25800,12 +25820,12 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
@@ -25930,7 +25950,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26260,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26289,12 +26309,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26360,7 +26380,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26409,12 +26429,12 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -26658,7 +26678,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -27092,7 +27112,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27146,7 +27166,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27216,7 +27236,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27260,17 +27280,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27634,7 +27654,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27990,7 +28010,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -28056,7 +28076,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28100,12 +28120,12 @@
       </c>
       <c r="AB224" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
@@ -28300,7 +28320,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28349,12 +28369,12 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28420,7 +28440,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28469,12 +28489,12 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -28598,7 +28618,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29160,7 +29180,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29214,7 +29234,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29346,7 +29366,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29590,7 +29610,7 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29676,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29717,12 +29737,12 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29970,7 +29990,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -30536,7 +30556,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30580,17 +30600,17 @@
       </c>
       <c r="AB244" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30858,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31032,7 +31052,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31081,12 +31101,12 @@
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -31206,7 +31226,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31768,7 +31788,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q254" s="2" t="inlineStr">
@@ -31812,17 +31832,17 @@
       </c>
       <c r="AB254" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC254" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32070,7 +32090,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32388,7 +32408,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32437,12 +32457,12 @@
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -32884,7 +32904,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32928,12 +32948,12 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33310,7 +33330,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33380,7 +33400,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33434,7 +33454,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33620,7 +33640,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33669,12 +33689,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33798,7 +33818,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34600,7 +34620,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34644,12 +34664,12 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -35026,7 +35046,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35096,7 +35116,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35150,7 +35170,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35390,7 +35410,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35460,7 +35480,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35509,12 +35529,12 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35828,7 +35848,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35872,17 +35892,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36324,7 +36344,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36368,12 +36388,12 @@
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
@@ -36502,7 +36522,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36545,24 +36565,24 @@
       </c>
       <c r="I293" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr"/>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N293" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O293" s="2" t="inlineStr">
@@ -36572,7 +36592,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36621,12 +36641,12 @@
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -36669,12 +36689,12 @@
       </c>
       <c r="I294" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K294" s="2" t="inlineStr"/>
@@ -36696,7 +36716,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36745,12 +36765,12 @@
       </c>
       <c r="AC294" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36816,7 +36836,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36870,7 +36890,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -36903,32 +36923,36 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N296" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O296" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -36936,7 +36960,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36960,17 +36984,17 @@
       </c>
       <c r="X296" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y296" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z296" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA296" s="2" t="inlineStr">
@@ -36980,17 +37004,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37023,32 +37047,36 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N297" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O297" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -37056,7 +37084,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37080,17 +37108,17 @@
       </c>
       <c r="X297" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA297" s="2" t="inlineStr">
@@ -37100,12 +37128,12 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
@@ -37176,7 +37204,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37225,12 +37253,12 @@
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -37296,7 +37324,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37350,7 +37378,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
